--- a/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者販売店一括置換画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者販売店一括置換画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1365,20 +1365,88 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>顧客要件（2026-07）対応：初期表示で購読者を自動読込しない旨を TC-006 に明記、選択時に表示されるのは置換先のみに TC-009 を修正、適用日を検索エリアの必須・未来日に TC-021/022 を再構成、置換可能条件（適用日での絞込）の TC-047 を追加</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6302,7 +6370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ64"/>
+  <dimension ref="A1:BQ65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8172,7 +8240,7 @@
       <c r="BP18" s="10" t="n"/>
       <c r="BQ18" s="11" t="n"/>
     </row>
-    <row r="19" ht="256" customHeight="1">
+    <row r="19" ht="336" customHeight="1">
       <c r="A19" s="44" t="n">
         <v>6</v>
       </c>
@@ -8263,7 +8331,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">検索フォームの各入力欄が空欄で表示されること、かつ結果テーブルに行が表示されないこと。
+            <t xml:space="preserve">検索フォームの各入力欄（適用日を含む）が空欄で表示されること、かつ結果テーブルに行が表示されないこと。「置換先配達販売店」欄は表示されないこと（検索結果を1件以上選択したときのみ表示）。
 </t>
           </r>
           <r>
@@ -8297,7 +8365,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・初期表示時にドロップダウンの読込以外のAPI呼び出しが発生しないこと。</t>
+            <t>・初期表示時にドロップダウンの読込以外のAPI呼び出しが発生しないこと（購読者検索APIは呼ばれない・顧客要件 2026-07）。</t>
           </r>
         </is>
       </c>
@@ -8711,7 +8779,7 @@
       <c r="BP21" s="10" t="n"/>
       <c r="BQ21" s="11" t="n"/>
     </row>
-    <row r="22" ht="272" customHeight="1">
+    <row r="22" ht="320" customHeight="1">
       <c r="A22" s="44" t="n">
         <v>9</v>
       </c>
@@ -8724,7 +8792,7 @@
       <c r="D22" s="11" t="n"/>
       <c r="E22" s="46" t="inlineStr">
         <is>
-          <t>チェック選択時に適用日と置換先が表示され検索ボタンが無効になること</t>
+          <t>チェック選択時に置換先が表示され検索ボタンが無効になること</t>
         </is>
       </c>
       <c r="F22" s="10" t="n"/>
@@ -8803,7 +8871,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「適用日」入力欄および「置換先配達販売店」ドロップダウンが表示され、いずれも必須項目となること。
+            <t xml:space="preserve">「置換先配達販売店」ドロップダウンが表示され、必須項目となること（「適用日」は検索エリアの必須項目として常時表示のため、選択時に新たに表示されるのは置換先のみ）。
 </t>
           </r>
           <r>
@@ -8837,7 +8905,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・全てのチェックを解除すると「適用日」「置換先配達販売店」が非表示となり、「検索」ボタンが再度有効になること。</t>
+            <t>・全てのチェックを解除すると「置換先配達販売店」が非表示となり、「検索」ボタンが再度有効になること（「適用日」は常時表示のまま）。</t>
           </r>
         </is>
       </c>
@@ -11011,7 +11079,7 @@
       <c r="BP35" s="10" t="n"/>
       <c r="BQ35" s="11" t="n"/>
     </row>
-    <row r="36" ht="224" customHeight="1">
+    <row r="36" ht="240" customHeight="1">
       <c r="A36" s="44" t="n">
         <v>21</v>
       </c>
@@ -11024,7 +11092,7 @@
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="46" t="inlineStr">
         <is>
-          <t>適用日未入力で必須エラーとなること</t>
+          <t>適用日未入力で検索できず必須エラーとなること</t>
         </is>
       </c>
       <c r="F36" s="10" t="n"/>
@@ -11034,8 +11102,7 @@
       <c r="J36" s="46" t="inlineStr">
         <is>
           <t>・role: CHUOKAI
-・ログイン済 + MFA認証済
-・検索結果一覧に購読者データが表示されている</t>
+・ログイン済 + MFA認証済</t>
         </is>
       </c>
       <c r="K36" s="10" t="n"/>
@@ -11060,7 +11127,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">任意の行のチェックボックスをオンにし、「置換先配達販売店」を選択する。
+            <t xml:space="preserve">購読者販売店一括置換画面を開く（初期表示では購読者一覧は自動読込されない）。
 </t>
           </r>
           <r>
@@ -11077,7 +11144,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>「適用日」を未入力のまま「置換処理実行」ボタンをクリックする。</t>
+            <t>「適用日」を未入力のまま（他の検索条件は任意）「検索」ボタンをクリックする。</t>
           </r>
         </is>
       </c>
@@ -11103,7 +11170,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「適用日」「置換先配達販売店」が表示され、置換先が選択されること。
+            <t xml:space="preserve">検索結果テーブルが空で表示されること。
 </t>
           </r>
           <r>
@@ -11120,7 +11187,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「適用日」欄にエラーとして「必須項目です。」が表示されること。
+            <t xml:space="preserve">「適用日」欄付近にエラーとして「適用日を入力してください。」（ACSMS-MSG-015-004 相当）が表示され、購読者検索APIが呼び出されないこと。
 </t>
           </r>
           <r>
@@ -11137,7 +11204,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・置換APIが呼び出されず、`t_dokusya` に変更が発生しないこと。</t>
+            <t>・適用日は検索エリアの必須項目（顧客要件 2026-07）。未入力では検索を実行しない。</t>
           </r>
         </is>
       </c>
@@ -11191,7 +11258,7 @@
       <c r="BP36" s="10" t="n"/>
       <c r="BQ36" s="11" t="n"/>
     </row>
-    <row r="37" ht="240" customHeight="1">
+    <row r="37" ht="352" customHeight="1">
       <c r="A37" s="44" t="n">
         <v>22</v>
       </c>
@@ -11204,7 +11271,7 @@
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="46" t="inlineStr">
         <is>
-          <t>適用日に過去日付を指定できないこと</t>
+          <t>適用日に当日・過去日付を指定できないこと（未来日のみ）</t>
         </is>
       </c>
       <c r="F37" s="10" t="n"/>
@@ -11215,7 +11282,6 @@
         <is>
           <t>・role: JA_HONTEN
 ・ログイン済 + MFA認証済
-・検索結果一覧に購読者データが表示されている
 ・当日が 2026-06-04 である</t>
         </is>
       </c>
@@ -11241,7 +11307,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">任意の行のチェックボックスをオンにし、「置換先配達販売店」を選択する。
+            <t xml:space="preserve">「適用日」に当日（2026-06-04）または過去日（2026-06-03）を指定して「検索」ボタンをクリックする。
 </t>
           </r>
           <r>
@@ -11258,7 +11324,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>「適用日」に当日より前の日付（2026-06-03）を指定して「置換処理実行」ボタンをクリックする。</t>
+            <t>「適用日」に翌日以降の未来日（2026-06-05）を指定して「検索」ボタンをクリックする。</t>
           </r>
         </is>
       </c>
@@ -11284,7 +11350,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「適用日」「置換先配達販売店」が表示され、置換先が選択されること。
+            <t xml:space="preserve">当日・過去日は選択不可となること（DatePicker で当日以前が非活性）、またはサーバー側で 400 (`DATE_RANGE_INVALID`, 「販売店適用日は本日より後の日付を入力してください。」) となり、購読者検索が実行されないこと。
 </t>
           </r>
           <r>
@@ -11301,7 +11367,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">過去日付が選択不可となること、またはサーバー側で当日以降のみ受理されること（適用日は当日以降のみ tekiyo_date &gt;= CURRENT_DATE）。
+            <t xml:space="preserve">未来日（2026-06-05）では検索が実行され、その適用日で置換可能な購読者一覧が表示されること。
 </t>
           </r>
           <r>
@@ -11318,7 +11384,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・当日（2026-06-04）以降の日付は正常に指定できること。</t>
+            <t>・適用日は**未来日のみ**（当日を含む過去日は不可・顧客要件 2026-07）。検索と置換実行で同一基準（`hanbaiten_tekiyo_date &gt; 当日(JST)`）。</t>
           </r>
         </is>
       </c>
@@ -16020,8 +16086,190 @@
       <c r="BP64" s="10" t="n"/>
       <c r="BQ64" s="11" t="n"/>
     </row>
+    <row r="65" ht="400" customHeight="1">
+      <c r="A65" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-015-047</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>適用日時点で置換可能な購読者のみが検索結果に表示されること</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="46" t="inlineStr">
+        <is>
+          <t>・role: CHUOKAI
+・ログイン済 + MFA認証済
+・購読者A: 購読開始日=2026-05-01、解約予定日=なし
+・購読者B: 購読開始日=2026-05-01、解約予定日=2026-08-01
+・購読者C: 購読開始日=2026-10-01（未来開始）、解約予定日=なし</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「適用日」に 2026-07-01 を指定して「検索」ボタンをクリックする。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>「適用日」に 2026-09-01 を指定して「検索」ボタンをクリックする。</t>
+          </r>
+        </is>
+      </c>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者A・Bが表示され、購読者C（購読開始日が適用日より後）は表示されないこと（置換可能条件：購読開始日 &lt;= 適用日）。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読者Aが表示され、購読者B（解約予定日 2026-08-01 &lt;= 適用日 2026-09-01）は表示されないこと。購読者C（購読開始日 2026-10-01 &gt; 適用日）も表示されないこと（置換可能条件：解約予定日が無い または 適用日より後）。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・置換可能条件は検索と置換実行で同一基準。ここで返る各行は個別に適用日で置換可能なため、任意の部分集合を選択して置換実行しても実行時チェックを通過する（顧客要件 2026-07）。</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+      <c r="AE65" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF65" s="11" t="n"/>
+      <c r="AG65" s="45" t="inlineStr"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="11" t="n"/>
+      <c r="AJ65" s="45" t="inlineStr"/>
+      <c r="AK65" s="10" t="n"/>
+      <c r="AL65" s="11" t="n"/>
+      <c r="AM65" s="45" t="inlineStr"/>
+      <c r="AN65" s="10" t="n"/>
+      <c r="AO65" s="11" t="n"/>
+      <c r="AP65" s="45" t="inlineStr"/>
+      <c r="AQ65" s="10" t="n"/>
+      <c r="AR65" s="11" t="n"/>
+      <c r="AS65" s="45" t="inlineStr"/>
+      <c r="AT65" s="10" t="n"/>
+      <c r="AU65" s="11" t="n"/>
+      <c r="AV65" s="45" t="inlineStr"/>
+      <c r="AW65" s="10" t="n"/>
+      <c r="AX65" s="11" t="n"/>
+      <c r="AY65" s="45" t="inlineStr"/>
+      <c r="AZ65" s="10" t="n"/>
+      <c r="BA65" s="11" t="n"/>
+      <c r="BB65" s="45" t="inlineStr"/>
+      <c r="BC65" s="10" t="n"/>
+      <c r="BD65" s="11" t="n"/>
+      <c r="BE65" s="45" t="inlineStr"/>
+      <c r="BF65" s="10" t="n"/>
+      <c r="BG65" s="11" t="n"/>
+      <c r="BH65" s="45" t="inlineStr"/>
+      <c r="BI65" s="10" t="n"/>
+      <c r="BJ65" s="11" t="n"/>
+      <c r="BK65" s="46" t="inlineStr"/>
+      <c r="BL65" s="10" t="n"/>
+      <c r="BM65" s="10" t="n"/>
+      <c r="BN65" s="10" t="n"/>
+      <c r="BO65" s="10" t="n"/>
+      <c r="BP65" s="10" t="n"/>
+      <c r="BQ65" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="855">
+  <mergeCells count="872">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -16054,6 +16302,7 @@
     <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
     <mergeCell ref="AM21:AO21"/>
+    <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
     <mergeCell ref="W2:AH2"/>
@@ -16115,6 +16364,7 @@
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
     <mergeCell ref="AS64:AU64"/>
+    <mergeCell ref="J65:P65"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
@@ -16220,6 +16470,7 @@
     <mergeCell ref="E36:I36"/>
     <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="AP24:AR24"/>
@@ -16272,6 +16523,7 @@
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="E26:I26"/>
     <mergeCell ref="AY37:BA37"/>
+    <mergeCell ref="BE65:BG65"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
     <mergeCell ref="J36:P36"/>
@@ -16287,6 +16539,7 @@
     <mergeCell ref="BH53:BJ53"/>
     <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="Q65:W65"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
     <mergeCell ref="AP63:AR63"/>
@@ -16301,6 +16554,7 @@
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
+    <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AS28:AU28"/>
@@ -16335,6 +16589,7 @@
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="AG65:AI65"/>
     <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
@@ -16365,6 +16620,7 @@
     <mergeCell ref="J52:P52"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="BB65:BD65"/>
     <mergeCell ref="E60:I60"/>
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="AV60:AX60"/>
@@ -16475,6 +16731,7 @@
     <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="B62:D62"/>
@@ -16520,6 +16777,7 @@
     <mergeCell ref="BB35:BD35"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
@@ -16583,6 +16841,7 @@
     <mergeCell ref="A25:BQ25"/>
     <mergeCell ref="E19:I19"/>
     <mergeCell ref="BE52:BG52"/>
+    <mergeCell ref="BK65:BQ65"/>
     <mergeCell ref="BK21:BQ21"/>
     <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
@@ -16662,6 +16921,7 @@
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
+    <mergeCell ref="BH65:BJ65"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -16706,6 +16966,7 @@
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="B54:D54"/>
+    <mergeCell ref="AE65:AF65"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="J27:P27"/>
@@ -16759,6 +17020,7 @@
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
+    <mergeCell ref="AY65:BA65"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="AY21:BA21"/>
@@ -16775,6 +17037,7 @@
     <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
+    <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
@@ -16802,6 +17065,7 @@
     <mergeCell ref="AG28:AI28"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
+    <mergeCell ref="B65:D65"/>
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
@@ -16852,6 +17116,7 @@
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
@@ -16879,13 +17144,13 @@
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE24 AE26:AE28 AE30:AE39 AE41:AE46 AE48:AE56 AE58:AE64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE24 AE26:AE28 AE30:AE39 AE41:AE46 AE48:AE56 AE58:AE65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG24 AG26:AG28 AG30:AG39 AG41:AG46 AG48:AG56 AG58:AG64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG24 AG26:AG28 AG30:AG39 AG41:AG46 AG48:AG56 AG58:AG65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV24 AV26:AV28 AV30:AV39 AV41:AV46 AV48:AV56 AV58:AV64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV24 AV26:AV28 AV30:AV39 AV41:AV46 AV48:AV56 AV58:AV65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者販売店一括置換画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者販売店一括置換画面_v1.0.xlsx
@@ -1611,7 +1611,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -1627,7 +1627,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -2102,7 +2102,7 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="H4" s="10" t="n"/>
@@ -2875,7 +2875,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -2891,7 +2891,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -6370,7 +6370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ65"/>
+  <dimension ref="A1:BQ66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6508,7 +6508,7 @@
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -11350,7 +11350,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">当日・過去日は選択不可となること（DatePicker で当日以前が非活性）、またはサーバー側で 400 (`DATE_RANGE_INVALID`, 「販売店適用日は本日より後の日付を入力してください。」) となり、購読者検索が実行されないこと。
+            <t xml:space="preserve">当日・過去日は選択不可となること（DatePicker で当日以前が非活性）、またはサーバー側で 400 (`DATE_RANGE_INVALID`, 「紙版の適用日は本日より後の日付を入力してください。」) となり、購読者検索が実行されないこと。
 </t>
           </r>
           <r>
@@ -11384,7 +11384,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・適用日は**未来日のみ**（当日を含む過去日は不可・顧客要件 2026-07）。検索と置換実行で同一基準（`hanbaiten_tekiyo_date &gt; 当日(JST)`）。</t>
+            <t>・適用日は**未来日のみ**（当日を含む過去日は不可・顧客要件 2026-07）。検索と置換実行で同一基準（`joho_henko_tekiyo_date &gt; 当日(JST)`）。</t>
           </r>
         </is>
       </c>
@@ -15253,7 +15253,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>dokusya_ids・new_hanbaiten_id・hanbaiten_tekiyo_date を未設定で送信する。</t>
+            <t>dokusya_ids・new_hanbaiten_id・joho_henko_tekiyo_date を未設定で送信する。</t>
           </r>
         </is>
       </c>
@@ -16268,8 +16268,222 @@
       <c r="BP65" s="10" t="n"/>
       <c r="BQ65" s="11" t="n"/>
     </row>
+    <row r="66" ht="450" customHeight="1">
+      <c r="A66" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B66" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-015-048</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="46" t="inlineStr">
+        <is>
+          <t>購読種別で電子版を選択した場合に対象外メッセージが表示され検索できないこと</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・ログイン済 + MFA認証済
+・購読種別ラジオに「紙版」「電子版」が表示される（併読は表示されない）</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="11" t="n"/>
+      <c r="Q66" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読種別で「電子版」ラジオを選択する。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">（電子版を選択したまま）「検索」ボタンの状態を確認する。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>購読種別を「紙版」に切り替える。</t>
+          </r>
+        </is>
+      </c>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="11" t="n"/>
+      <c r="X66" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">トースト通知に「電子版は本画面では対象外です。」（ACSMS-MSG-015-009）が表示されること（フォーム内インラインメッセージは表示しない）。適用日はクリアされ入力不可（非活性）のままであること。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「検索」ボタンが非活性（disabled）となり、購読者検索APIが呼び出されないこと。仮にAPIを直接呼び出した場合はサーバー側で 400 (`VALIDATION_ERROR`, errors=[{ field: "dokusya_shubetsu", message: "電子版は本画面では対象外です。" }]) となること（防御的サーバ側ガード）。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「電子版は本画面では対象外です。」メッセージが消え、適用日がカレンダー入力可（活性）となり、「検索」ボタンが再度活性になること。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・電子版=電子配信で販売店を持たないため一括置換の対象外（顧客要件 2026-07 改訂で「電子版=当日置換」を撤回）。ラジオ自体は選択可能とし、選択時にトーストで対象外を通知する（インラインメッセージは出さない）。検索・置換実行の両APIとも `dokusya_shubetsu=2` は日付に関係なく拒否する。</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="11" t="n"/>
+      <c r="AE66" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF66" s="11" t="n"/>
+      <c r="AG66" s="45" t="inlineStr"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="11" t="n"/>
+      <c r="AJ66" s="45" t="inlineStr"/>
+      <c r="AK66" s="10" t="n"/>
+      <c r="AL66" s="11" t="n"/>
+      <c r="AM66" s="45" t="inlineStr"/>
+      <c r="AN66" s="10" t="n"/>
+      <c r="AO66" s="11" t="n"/>
+      <c r="AP66" s="45" t="inlineStr"/>
+      <c r="AQ66" s="10" t="n"/>
+      <c r="AR66" s="11" t="n"/>
+      <c r="AS66" s="45" t="inlineStr"/>
+      <c r="AT66" s="10" t="n"/>
+      <c r="AU66" s="11" t="n"/>
+      <c r="AV66" s="45" t="inlineStr"/>
+      <c r="AW66" s="10" t="n"/>
+      <c r="AX66" s="11" t="n"/>
+      <c r="AY66" s="45" t="inlineStr"/>
+      <c r="AZ66" s="10" t="n"/>
+      <c r="BA66" s="11" t="n"/>
+      <c r="BB66" s="45" t="inlineStr"/>
+      <c r="BC66" s="10" t="n"/>
+      <c r="BD66" s="11" t="n"/>
+      <c r="BE66" s="45" t="inlineStr"/>
+      <c r="BF66" s="10" t="n"/>
+      <c r="BG66" s="11" t="n"/>
+      <c r="BH66" s="45" t="inlineStr"/>
+      <c r="BI66" s="10" t="n"/>
+      <c r="BJ66" s="11" t="n"/>
+      <c r="BK66" s="46" t="inlineStr"/>
+      <c r="BL66" s="10" t="n"/>
+      <c r="BM66" s="10" t="n"/>
+      <c r="BN66" s="10" t="n"/>
+      <c r="BO66" s="10" t="n"/>
+      <c r="BP66" s="10" t="n"/>
+      <c r="BQ66" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="872">
+  <mergeCells count="889">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -16353,11 +16567,13 @@
     <mergeCell ref="AE64:AF64"/>
     <mergeCell ref="AS62:AU62"/>
     <mergeCell ref="AV63:AX63"/>
+    <mergeCell ref="AP66:AR66"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AP28:AR28"/>
+    <mergeCell ref="BK66:BQ66"/>
     <mergeCell ref="BK53:BQ53"/>
     <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
@@ -16451,6 +16667,7 @@
     <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="X27:AD27"/>
+    <mergeCell ref="AG66:AI66"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="AY60:BA60"/>
@@ -16530,6 +16747,7 @@
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
+    <mergeCell ref="AY66:BA66"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
@@ -16585,6 +16803,7 @@
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
+    <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
@@ -16621,6 +16840,7 @@
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="AV37:AX37"/>
     <mergeCell ref="BB65:BD65"/>
+    <mergeCell ref="BE66:BG66"/>
     <mergeCell ref="E60:I60"/>
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="AV60:AX60"/>
@@ -16638,6 +16858,7 @@
     <mergeCell ref="AM42:AO42"/>
     <mergeCell ref="X62:AD62"/>
     <mergeCell ref="AE37:AF37"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="BB19:BD19"/>
     <mergeCell ref="AM23:AO23"/>
@@ -16694,6 +16915,7 @@
     <mergeCell ref="AM46:AO46"/>
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="E66:I66"/>
     <mergeCell ref="E53:I53"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
@@ -16736,6 +16958,7 @@
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="AG35:AI35"/>
+    <mergeCell ref="AV66:AX66"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
@@ -16764,6 +16987,7 @@
     <mergeCell ref="AP51:AR51"/>
     <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK64:BQ64"/>
+    <mergeCell ref="J66:P66"/>
     <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="X60:AD60"/>
     <mergeCell ref="AM61:AO61"/>
@@ -16829,6 +17053,7 @@
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="AE66:AF66"/>
     <mergeCell ref="Q45:W45"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
@@ -16840,6 +17065,7 @@
     <mergeCell ref="BH13:BJ13"/>
     <mergeCell ref="A25:BQ25"/>
     <mergeCell ref="E19:I19"/>
+    <mergeCell ref="AS66:AU66"/>
     <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BK65:BQ65"/>
     <mergeCell ref="BK21:BQ21"/>
@@ -16932,6 +17158,7 @@
     <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="AY62:BA62"/>
     <mergeCell ref="BB63:BD63"/>
+    <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
@@ -16941,6 +17168,7 @@
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
     <mergeCell ref="AV19:AX19"/>
+    <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
     <mergeCell ref="AY51:BA51"/>
@@ -17025,6 +17253,7 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="E61:I61"/>
+    <mergeCell ref="BB66:BD66"/>
     <mergeCell ref="A29:BQ29"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
@@ -17038,6 +17267,7 @@
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
     <mergeCell ref="X65:AD65"/>
+    <mergeCell ref="AM66:AO66"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
@@ -17121,6 +17351,7 @@
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
     <mergeCell ref="BH64:BJ64"/>
+    <mergeCell ref="X66:AD66"/>
     <mergeCell ref="BE19:BG19"/>
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AM33:AO33"/>
@@ -17144,13 +17375,13 @@
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE24 AE26:AE28 AE30:AE39 AE41:AE46 AE48:AE56 AE58:AE65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE24 AE26:AE28 AE30:AE39 AE41:AE46 AE48:AE56 AE58:AE66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG24 AG26:AG28 AG30:AG39 AG41:AG46 AG48:AG56 AG58:AG65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG24 AG26:AG28 AG30:AG39 AG41:AG46 AG48:AG56 AG58:AG66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV24 AV26:AV28 AV30:AV39 AV41:AV46 AV48:AV56 AV58:AV65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV24 AV26:AV28 AV30:AV39 AV41:AV46 AV48:AV56 AV58:AV66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者販売店一括置換画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-015/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者販売店一括置換画面_v1.0.xlsx
@@ -1611,7 +1611,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -1627,7 +1627,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -2102,7 +2102,7 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="H4" s="10" t="n"/>
@@ -2875,7 +2875,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -2891,7 +2891,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -6370,7 +6370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ66"/>
+  <dimension ref="A1:BQ69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6508,7 +6508,7 @@
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -16086,181 +16086,74 @@
       <c r="BP64" s="10" t="n"/>
       <c r="BQ64" s="11" t="n"/>
     </row>
-    <row r="65" ht="400" customHeight="1">
-      <c r="A65" s="44" t="n">
-        <v>47</v>
-      </c>
-      <c r="B65" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-015-047</t>
-        </is>
-      </c>
+    <row r="65" ht="22.5" customHeight="1">
+      <c r="A65" s="32" t="inlineStr">
+        <is>
+          <t>業務ロジック — as-of 判定・置換先条件（Function — As-of / Destination）</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="n"/>
       <c r="C65" s="10" t="n"/>
-      <c r="D65" s="11" t="n"/>
-      <c r="E65" s="46" t="inlineStr">
-        <is>
-          <t>適用日時点で置換可能な購読者のみが検索結果に表示されること</t>
-        </is>
-      </c>
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
       <c r="F65" s="10" t="n"/>
       <c r="G65" s="10" t="n"/>
       <c r="H65" s="10" t="n"/>
-      <c r="I65" s="11" t="n"/>
-      <c r="J65" s="46" t="inlineStr">
-        <is>
-          <t>・role: CHUOKAI
-・ログイン済 + MFA認証済
-・購読者A: 購読開始日=2026-05-01、解約予定日=なし
-・購読者B: 購読開始日=2026-05-01、解約予定日=2026-08-01
-・購読者C: 購読開始日=2026-10-01（未来開始）、解約予定日=なし</t>
-        </is>
-      </c>
+      <c r="I65" s="10" t="n"/>
+      <c r="J65" s="10" t="n"/>
       <c r="K65" s="10" t="n"/>
       <c r="L65" s="10" t="n"/>
       <c r="M65" s="10" t="n"/>
       <c r="N65" s="10" t="n"/>
       <c r="O65" s="10" t="n"/>
-      <c r="P65" s="11" t="n"/>
-      <c r="Q65" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">「適用日」に 2026-07-01 を指定して「検索」ボタンをクリックする。
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>「適用日」に 2026-09-01 を指定して「検索」ボタンをクリックする。</t>
-          </r>
-        </is>
-      </c>
+      <c r="P65" s="10" t="n"/>
+      <c r="Q65" s="10" t="n"/>
       <c r="R65" s="10" t="n"/>
       <c r="S65" s="10" t="n"/>
       <c r="T65" s="10" t="n"/>
       <c r="U65" s="10" t="n"/>
       <c r="V65" s="10" t="n"/>
-      <c r="W65" s="11" t="n"/>
-      <c r="X65" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">購読者A・Bが表示され、購読者C（購読開始日が適用日より後）は表示されないこと（置換可能条件：購読開始日 &lt;= 適用日）。
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">購読者Aが表示され、購読者B（解約予定日 2026-08-01 &lt;= 適用日 2026-09-01）は表示されないこと。購読者C（購読開始日 2026-10-01 &gt; 適用日）も表示されないこと（置換可能条件：解約予定日が無い または 適用日より後）。
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・置換可能条件は検索と置換実行で同一基準。ここで返る各行は個別に適用日で置換可能なため、任意の部分集合を選択して置換実行しても実行時チェックを通過する（顧客要件 2026-07）。</t>
-          </r>
-        </is>
-      </c>
+      <c r="W65" s="10" t="n"/>
+      <c r="X65" s="10" t="n"/>
       <c r="Y65" s="10" t="n"/>
       <c r="Z65" s="10" t="n"/>
       <c r="AA65" s="10" t="n"/>
       <c r="AB65" s="10" t="n"/>
       <c r="AC65" s="10" t="n"/>
-      <c r="AD65" s="11" t="n"/>
-      <c r="AE65" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF65" s="11" t="n"/>
-      <c r="AG65" s="45" t="inlineStr"/>
+      <c r="AD65" s="10" t="n"/>
+      <c r="AE65" s="10" t="n"/>
+      <c r="AF65" s="10" t="n"/>
+      <c r="AG65" s="10" t="n"/>
       <c r="AH65" s="10" t="n"/>
-      <c r="AI65" s="11" t="n"/>
-      <c r="AJ65" s="45" t="inlineStr"/>
+      <c r="AI65" s="10" t="n"/>
+      <c r="AJ65" s="10" t="n"/>
       <c r="AK65" s="10" t="n"/>
-      <c r="AL65" s="11" t="n"/>
-      <c r="AM65" s="45" t="inlineStr"/>
+      <c r="AL65" s="10" t="n"/>
+      <c r="AM65" s="10" t="n"/>
       <c r="AN65" s="10" t="n"/>
-      <c r="AO65" s="11" t="n"/>
-      <c r="AP65" s="45" t="inlineStr"/>
+      <c r="AO65" s="10" t="n"/>
+      <c r="AP65" s="10" t="n"/>
       <c r="AQ65" s="10" t="n"/>
-      <c r="AR65" s="11" t="n"/>
-      <c r="AS65" s="45" t="inlineStr"/>
+      <c r="AR65" s="10" t="n"/>
+      <c r="AS65" s="10" t="n"/>
       <c r="AT65" s="10" t="n"/>
-      <c r="AU65" s="11" t="n"/>
-      <c r="AV65" s="45" t="inlineStr"/>
+      <c r="AU65" s="10" t="n"/>
+      <c r="AV65" s="10" t="n"/>
       <c r="AW65" s="10" t="n"/>
-      <c r="AX65" s="11" t="n"/>
-      <c r="AY65" s="45" t="inlineStr"/>
+      <c r="AX65" s="10" t="n"/>
+      <c r="AY65" s="10" t="n"/>
       <c r="AZ65" s="10" t="n"/>
-      <c r="BA65" s="11" t="n"/>
-      <c r="BB65" s="45" t="inlineStr"/>
+      <c r="BA65" s="10" t="n"/>
+      <c r="BB65" s="10" t="n"/>
       <c r="BC65" s="10" t="n"/>
-      <c r="BD65" s="11" t="n"/>
-      <c r="BE65" s="45" t="inlineStr"/>
+      <c r="BD65" s="10" t="n"/>
+      <c r="BE65" s="10" t="n"/>
       <c r="BF65" s="10" t="n"/>
-      <c r="BG65" s="11" t="n"/>
-      <c r="BH65" s="45" t="inlineStr"/>
+      <c r="BG65" s="10" t="n"/>
+      <c r="BH65" s="10" t="n"/>
       <c r="BI65" s="10" t="n"/>
-      <c r="BJ65" s="11" t="n"/>
-      <c r="BK65" s="46" t="inlineStr"/>
+      <c r="BJ65" s="10" t="n"/>
+      <c r="BK65" s="10" t="n"/>
       <c r="BL65" s="10" t="n"/>
       <c r="BM65" s="10" t="n"/>
       <c r="BN65" s="10" t="n"/>
@@ -16268,20 +16161,20 @@
       <c r="BP65" s="10" t="n"/>
       <c r="BQ65" s="11" t="n"/>
     </row>
-    <row r="66" ht="450" customHeight="1">
+    <row r="66" ht="400" customHeight="1">
       <c r="A66" s="44" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B66" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-015-048</t>
+          <t>ACSMS-TC-015-047</t>
         </is>
       </c>
       <c r="C66" s="10" t="n"/>
       <c r="D66" s="11" t="n"/>
       <c r="E66" s="46" t="inlineStr">
         <is>
-          <t>購読種別で電子版を選択した場合に対象外メッセージが表示され検索できないこと</t>
+          <t>適用日時点で置換可能な購読者のみが検索結果に表示されること</t>
         </is>
       </c>
       <c r="F66" s="10" t="n"/>
@@ -16290,9 +16183,11 @@
       <c r="I66" s="11" t="n"/>
       <c r="J66" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN
+          <t>・role: CHUOKAI
 ・ログイン済 + MFA認証済
-・購読種別ラジオに「紙版」「電子版」が表示される（併読は表示されない）</t>
+・購読者A: 購読開始日=2026-05-01、解約予定日=なし
+・購読者B: 購読開始日=2026-05-01、解約予定日=2026-08-01
+・購読者C: 購読開始日=2026-10-01（未来開始）、解約予定日=なし</t>
         </is>
       </c>
       <c r="K66" s="10" t="n"/>
@@ -16317,7 +16212,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">購読種別で「電子版」ラジオを選択する。
+            <t xml:space="preserve">「適用日」に 2026-07-01 を指定して「検索」ボタンをクリックする。
 </t>
           </r>
           <r>
@@ -16334,24 +16229,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">（電子版を選択したまま）「検索」ボタンの状態を確認する。
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>購読種別を「紙版」に切り替える。</t>
+            <t>「適用日」に 2026-09-01 を指定して「検索」ボタンをクリックする。</t>
           </r>
         </is>
       </c>
@@ -16377,7 +16255,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">トースト通知に「電子版は本画面では対象外です。」（ACSMS-MSG-015-009）が表示されること（フォーム内インラインメッセージは表示しない）。適用日はクリアされ入力不可（非活性）のままであること。
+            <t xml:space="preserve">購読者A・Bが表示され、購読者C（購読開始日が適用日より後）は表示されないこと（置換可能条件：購読開始日 &lt;= 適用日）。
 </t>
           </r>
           <r>
@@ -16394,24 +16272,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「検索」ボタンが非活性（disabled）となり、購読者検索APIが呼び出されないこと。仮にAPIを直接呼び出した場合はサーバー側で 400 (`VALIDATION_ERROR`, errors=[{ field: "dokusya_shubetsu", message: "電子版は本画面では対象外です。" }]) となること（防御的サーバ側ガード）。
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">「電子版は本画面では対象外です。」メッセージが消え、適用日がカレンダー入力可（活性）となり、「検索」ボタンが再度活性になること。
+            <t xml:space="preserve">購読者Aが表示され、購読者B（解約予定日 2026-08-01 &lt;= 適用日 2026-09-01）は表示されないこと。購読者C（購読開始日 2026-10-01 &gt; 適用日）も表示されないこと（置換可能条件：解約予定日が無い または 適用日より後）。
 </t>
           </r>
           <r>
@@ -16428,7 +16289,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・電子版=電子配信で販売店を持たないため一括置換の対象外（顧客要件 2026-07 改訂で「電子版=当日置換」を撤回）。ラジオ自体は選択可能とし、選択時にトーストで対象外を通知する（インラインメッセージは出さない）。検索・置換実行の両APIとも `dokusya_shubetsu=2` は日付に関係なく拒否する。</t>
+            <t>・置換可能条件は検索と置換実行で同一基準。ここで返る各行は個別に適用日で置換可能なため、任意の部分集合を選択して置換実行しても実行時チェックを通過する（顧客要件 2026-07）。</t>
           </r>
         </is>
       </c>
@@ -16482,8 +16343,774 @@
       <c r="BP66" s="10" t="n"/>
       <c r="BQ66" s="11" t="n"/>
     </row>
+    <row r="67" ht="450" customHeight="1">
+      <c r="A67" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B67" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-015-048</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>購読種別で電子版を選択した場合に対象外メッセージが表示され検索できないこと</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・ログイン済 + MFA認証済
+・購読種別ラジオに「紙版」「電子版」が表示される（併読は表示されない）</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="11" t="n"/>
+      <c r="Q67" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読種別で「電子版」ラジオを選択する。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">（電子版を選択したまま）「検索」ボタンの状態を確認する。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>購読種別を「紙版」に切り替える。</t>
+          </r>
+        </is>
+      </c>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="11" t="n"/>
+      <c r="X67" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">トースト通知に「電子版は本画面では対象外です。」（ACSMS-MSG-015-009）が表示されること（フォーム内インラインメッセージは表示しない）。適用日はクリアされ入力不可（非活性）のままであること。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「検索」ボタンが非活性（disabled）となり、購読者検索APIが呼び出されないこと。仮にAPIを直接呼び出した場合はサーバー側で 400 (`VALIDATION_ERROR`, errors=[{ field: "dokusya_shubetsu", message: "電子版は本画面では対象外です。" }]) となること（防御的サーバ側ガード）。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「電子版は本画面では対象外です。」メッセージが消え、適用日がカレンダー入力可（活性）となり、「検索」ボタンが再度活性になること。
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・電子版=電子配信で販売店を持たないため一括置換の対象外（顧客要件 2026-07 改訂で「電子版=当日置換」を撤回）。ラジオ自体は選択可能とし、選択時にトーストで対象外を通知する（インラインメッセージは出さない）。検索・置換実行の両APIとも `dokusya_shubetsu=2` は日付に関係なく拒否する。</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="11" t="n"/>
+      <c r="AE67" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF67" s="11" t="n"/>
+      <c r="AG67" s="45" t="inlineStr"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="11" t="n"/>
+      <c r="AJ67" s="45" t="inlineStr"/>
+      <c r="AK67" s="10" t="n"/>
+      <c r="AL67" s="11" t="n"/>
+      <c r="AM67" s="45" t="inlineStr"/>
+      <c r="AN67" s="10" t="n"/>
+      <c r="AO67" s="11" t="n"/>
+      <c r="AP67" s="45" t="inlineStr"/>
+      <c r="AQ67" s="10" t="n"/>
+      <c r="AR67" s="11" t="n"/>
+      <c r="AS67" s="45" t="inlineStr"/>
+      <c r="AT67" s="10" t="n"/>
+      <c r="AU67" s="11" t="n"/>
+      <c r="AV67" s="45" t="inlineStr"/>
+      <c r="AW67" s="10" t="n"/>
+      <c r="AX67" s="11" t="n"/>
+      <c r="AY67" s="45" t="inlineStr"/>
+      <c r="AZ67" s="10" t="n"/>
+      <c r="BA67" s="11" t="n"/>
+      <c r="BB67" s="45" t="inlineStr"/>
+      <c r="BC67" s="10" t="n"/>
+      <c r="BD67" s="11" t="n"/>
+      <c r="BE67" s="45" t="inlineStr"/>
+      <c r="BF67" s="10" t="n"/>
+      <c r="BG67" s="11" t="n"/>
+      <c r="BH67" s="45" t="inlineStr"/>
+      <c r="BI67" s="10" t="n"/>
+      <c r="BJ67" s="11" t="n"/>
+      <c r="BK67" s="46" t="inlineStr"/>
+      <c r="BL67" s="10" t="n"/>
+      <c r="BM67" s="10" t="n"/>
+      <c r="BN67" s="10" t="n"/>
+      <c r="BO67" s="10" t="n"/>
+      <c r="BP67" s="10" t="n"/>
+      <c r="BQ67" s="11" t="n"/>
+    </row>
+    <row r="68" ht="450" customHeight="1">
+      <c r="A68" s="44" t="n">
+        <v>49</v>
+      </c>
+      <c r="B68" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-015-049</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="46" t="inlineStr">
+        <is>
+          <t>置換先配達販売店が検索条件（必須）であり、既に置換先を配達している購読者が除外されること</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`dokusya.replace_hanbaiten` 権限あり）
+・購読種別=紙版・購読中の購読者が以下のとおり存在すること（適用日を 2030/09/01 とする）
+・(a) 適用日時点の有効履歴の配達販売店 = 販売店A（置換元）が 3 件
+・(b) 適用日時点の有効履歴の配達販売店 = 販売店B（置換先）が 2 件
+・(c) 適用日時点の有効履歴の配達販売店 = 販売店C（A でも B でもない）が 2 件</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="11" t="n"/>
+      <c r="Q68" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">検索エリアの項目配置を確認する（適用日の直後に「置換先配達販売店」があること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">置換先配達販売店を未選択のまま「検索」をクリックする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読種別=紙版・適用日=2030/09/01・配達販売店=販売店A・置換先配達販売店=販売店B で検索する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">配達販売店=販売店B・置換先配達販売店=販売店B で検索する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>検索結果を選択して「置換」を実行し、置換先が検索条件で選んだ販売店Bになることを確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
+      <c r="U68" s="10" t="n"/>
+      <c r="V68" s="10" t="n"/>
+      <c r="W68" s="11" t="n"/>
+      <c r="X68" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「置換先配達販売店」が検索エリアの適用日の直後に常時表示されること。検索結果選択後に表示していた置換先入力欄は存在しないこと（顧客要件2026-07 で廃止）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ACSMS-MSG-015-010 `置換先配達販売店を選択してください。` が置換先フィールドの直下に表示され、APIが呼ばれないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(a) の 3 件のみが表示されること。(b) の 2 件は `eff.hanbaiten_id &lt;&gt; :new_hanbaiten_id` により**除外**されること。(c) の 2 件は配達販売店の絞り込みにより対象外であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ACSMS-MSG-015-011 `配達販売店と置換先配達販売店が同じです。異なる販売店を選択してください。` が表示され、APIが呼ばれないこと。仮に API を直接呼び出した場合は 0 件が返ること（`eff.hanbaiten_id = B` かつ `eff.hanbaiten_id &lt;&gt; B` は同時に成立しないため）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">検索条件で選択した置換先（販売店B）がそのまま置換実行のターゲットになること。置換後 ACSMS-MSG-015-008 `置換処理が完了しました。` が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・置換先を検索条件へ移動し、同じ値を置換ターゲットとして使う仕様（顧客要件2026-07・API設計書 v1.7）。「検索した集合」と「置換先」が別入力だった従来仕様では、検索後に置換先を変え、既にその販売店を配達している購読者を含んだまま置換できてしまう余地があった
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・除外条件は master ではなく **適用日時点で有効な履歴レコード**で判定する（未来の適用日でも正しい母集合を返す）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y68" s="10" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
+      <c r="AB68" s="10" t="n"/>
+      <c r="AC68" s="10" t="n"/>
+      <c r="AD68" s="11" t="n"/>
+      <c r="AE68" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF68" s="11" t="n"/>
+      <c r="AG68" s="45" t="inlineStr"/>
+      <c r="AH68" s="10" t="n"/>
+      <c r="AI68" s="11" t="n"/>
+      <c r="AJ68" s="45" t="inlineStr"/>
+      <c r="AK68" s="10" t="n"/>
+      <c r="AL68" s="11" t="n"/>
+      <c r="AM68" s="45" t="inlineStr"/>
+      <c r="AN68" s="10" t="n"/>
+      <c r="AO68" s="11" t="n"/>
+      <c r="AP68" s="45" t="inlineStr"/>
+      <c r="AQ68" s="10" t="n"/>
+      <c r="AR68" s="11" t="n"/>
+      <c r="AS68" s="45" t="inlineStr"/>
+      <c r="AT68" s="10" t="n"/>
+      <c r="AU68" s="11" t="n"/>
+      <c r="AV68" s="45" t="inlineStr"/>
+      <c r="AW68" s="10" t="n"/>
+      <c r="AX68" s="11" t="n"/>
+      <c r="AY68" s="45" t="inlineStr"/>
+      <c r="AZ68" s="10" t="n"/>
+      <c r="BA68" s="11" t="n"/>
+      <c r="BB68" s="45" t="inlineStr"/>
+      <c r="BC68" s="10" t="n"/>
+      <c r="BD68" s="11" t="n"/>
+      <c r="BE68" s="45" t="inlineStr"/>
+      <c r="BF68" s="10" t="n"/>
+      <c r="BG68" s="11" t="n"/>
+      <c r="BH68" s="45" t="inlineStr"/>
+      <c r="BI68" s="10" t="n"/>
+      <c r="BJ68" s="11" t="n"/>
+      <c r="BK68" s="46" t="inlineStr"/>
+      <c r="BL68" s="10" t="n"/>
+      <c r="BM68" s="10" t="n"/>
+      <c r="BN68" s="10" t="n"/>
+      <c r="BO68" s="10" t="n"/>
+      <c r="BP68" s="10" t="n"/>
+      <c r="BQ68" s="11" t="n"/>
+    </row>
+    <row r="69" ht="450" customHeight="1">
+      <c r="A69" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="B69" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-015-050</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="46" t="inlineStr">
+        <is>
+          <t>配達販売店（置換元）が任意であり、未指定時は置換先以外の全販売店が対象となること</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`dokusya.replace_hanbaiten` 権限あり）
+・ACSMS-TC-015-049 と同じデータ（販売店A 3件・販売店B 2件・販売店C 2件）</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="11" t="n"/>
+      <c r="Q69" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">検索エリアの「配達販売店」のラベルと必須マークの有無を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">配達販売店を**未指定**のまま、購読種別=紙版・適用日=2030/09/01・置換先配達販売店=販売店B で検索する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">配達販売店=販売店A を指定して同じ条件で検索し、ステップ2との差分を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>配達販売店を未指定のまま検索した結果を全選択して置換を実行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="11" t="n"/>
+      <c r="X69" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ラベルが「配達販売店」（「置換元配達販売店」ではない）であり、必須マーク（`*`）が付いていないこと（顧客要件2026-07 改訂で必須→任意へ戻した）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店A の 3 件と販売店C の 2 件、計 5 件が表示されること（置換先=販売店B 以外の全販売店が対象）。販売店B の 2 件は除外されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店A の 3 件のみが表示されること（`eff.hanbaiten_id = :hanbaiten_id` が追加で効く）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店A・販売店C の購読者がまとめて販売店B へ置換されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・配達販売店は「指定時のみ絞り込む」条件。未指定でも `≠ 置換先` は常に適用されるため、置換先を配達中の購読者が混入することはない（API設計書 v1.8・§4.3）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・複数の置換元から1つの置換先へまとめる運用のための改訂。必須のままでは販売店ごとに検索・置換を繰り返す必要があった</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="11" t="n"/>
+      <c r="AE69" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF69" s="11" t="n"/>
+      <c r="AG69" s="45" t="inlineStr"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="11" t="n"/>
+      <c r="AJ69" s="45" t="inlineStr"/>
+      <c r="AK69" s="10" t="n"/>
+      <c r="AL69" s="11" t="n"/>
+      <c r="AM69" s="45" t="inlineStr"/>
+      <c r="AN69" s="10" t="n"/>
+      <c r="AO69" s="11" t="n"/>
+      <c r="AP69" s="45" t="inlineStr"/>
+      <c r="AQ69" s="10" t="n"/>
+      <c r="AR69" s="11" t="n"/>
+      <c r="AS69" s="45" t="inlineStr"/>
+      <c r="AT69" s="10" t="n"/>
+      <c r="AU69" s="11" t="n"/>
+      <c r="AV69" s="45" t="inlineStr"/>
+      <c r="AW69" s="10" t="n"/>
+      <c r="AX69" s="11" t="n"/>
+      <c r="AY69" s="45" t="inlineStr"/>
+      <c r="AZ69" s="10" t="n"/>
+      <c r="BA69" s="11" t="n"/>
+      <c r="BB69" s="45" t="inlineStr"/>
+      <c r="BC69" s="10" t="n"/>
+      <c r="BD69" s="11" t="n"/>
+      <c r="BE69" s="45" t="inlineStr"/>
+      <c r="BF69" s="10" t="n"/>
+      <c r="BG69" s="11" t="n"/>
+      <c r="BH69" s="45" t="inlineStr"/>
+      <c r="BI69" s="10" t="n"/>
+      <c r="BJ69" s="11" t="n"/>
+      <c r="BK69" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL69" s="10" t="n"/>
+      <c r="BM69" s="10" t="n"/>
+      <c r="BN69" s="10" t="n"/>
+      <c r="BO69" s="10" t="n"/>
+      <c r="BP69" s="10" t="n"/>
+      <c r="BQ69" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="889">
+  <mergeCells count="924">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -16516,7 +17143,6 @@
     <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
     <mergeCell ref="AM21:AO21"/>
-    <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
     <mergeCell ref="W2:AH2"/>
@@ -16529,6 +17155,7 @@
     <mergeCell ref="Q38:W38"/>
     <mergeCell ref="AE34:AF34"/>
     <mergeCell ref="AJ51:AL51"/>
+    <mergeCell ref="X68:AD68"/>
     <mergeCell ref="AE36:AF36"/>
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
@@ -16543,18 +17170,21 @@
     <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
     <mergeCell ref="AG52:AI52"/>
+    <mergeCell ref="X69:AD69"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="BB26:BD26"/>
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AJ33:AL33"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="X21:AD21"/>
     <mergeCell ref="AE62:AF62"/>
+    <mergeCell ref="B68:D68"/>
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="BB27:BD27"/>
     <mergeCell ref="AY31:BA31"/>
@@ -16580,11 +17210,12 @@
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
     <mergeCell ref="AS64:AU64"/>
-    <mergeCell ref="J65:P65"/>
+    <mergeCell ref="AP68:AR68"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
+    <mergeCell ref="AP67:AR67"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="AM58:AO58"/>
@@ -16649,21 +17280,28 @@
     <mergeCell ref="Q34:W34"/>
     <mergeCell ref="X24:AD24"/>
     <mergeCell ref="BB43:BD43"/>
+    <mergeCell ref="BK68:BQ68"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
     <mergeCell ref="BE54:BG54"/>
+    <mergeCell ref="AJ67:AL67"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="BK67:BQ67"/>
     <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AP69:AR69"/>
     <mergeCell ref="AP44:AR44"/>
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="BE56:BG56"/>
+    <mergeCell ref="AJ69:AL69"/>
+    <mergeCell ref="BK69:BQ69"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="AV68:AX68"/>
     <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="X27:AD27"/>
@@ -16677,17 +17315,18 @@
     <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
+    <mergeCell ref="AG68:AI68"/>
     <mergeCell ref="AG43:AI43"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E49:I49"/>
+    <mergeCell ref="J68:P68"/>
     <mergeCell ref="Q64:W64"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
     <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="AP24:AR24"/>
@@ -16740,9 +17379,9 @@
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="E26:I26"/>
     <mergeCell ref="AY37:BA37"/>
-    <mergeCell ref="BE65:BG65"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
+    <mergeCell ref="AE68:AF68"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
@@ -16757,7 +17396,7 @@
     <mergeCell ref="BH53:BJ53"/>
     <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="A8:G8"/>
-    <mergeCell ref="Q65:W65"/>
+    <mergeCell ref="AY68:BA68"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
     <mergeCell ref="AP63:AR63"/>
@@ -16772,7 +17411,6 @@
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
-    <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AS28:AU28"/>
@@ -16808,7 +17446,6 @@
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="AG65:AI65"/>
     <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
@@ -16819,6 +17456,7 @@
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
+    <mergeCell ref="BH68:BJ68"/>
     <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
@@ -16830,18 +17468,21 @@
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
+    <mergeCell ref="BH67:BJ67"/>
     <mergeCell ref="J42:P42"/>
     <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="AY67:BA67"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
     <mergeCell ref="J52:P52"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="AV37:AX37"/>
-    <mergeCell ref="BB65:BD65"/>
     <mergeCell ref="BE66:BG66"/>
+    <mergeCell ref="AY69:BA69"/>
     <mergeCell ref="E60:I60"/>
+    <mergeCell ref="X67:AD67"/>
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
@@ -16874,6 +17515,7 @@
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B67:D67"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
@@ -16883,6 +17525,7 @@
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
     <mergeCell ref="BB60:BD60"/>
+    <mergeCell ref="B69:D69"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
@@ -16906,6 +17549,7 @@
     <mergeCell ref="AP56:AR56"/>
     <mergeCell ref="AG20:AI20"/>
     <mergeCell ref="B16:D16"/>
+    <mergeCell ref="BE68:BG68"/>
     <mergeCell ref="AP43:AR43"/>
     <mergeCell ref="AM53:AO53"/>
     <mergeCell ref="B10:D11"/>
@@ -16919,12 +17563,14 @@
     <mergeCell ref="E53:I53"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
+    <mergeCell ref="E68:I68"/>
     <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="AM44:AO44"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
+    <mergeCell ref="E67:I67"/>
     <mergeCell ref="AY14:BA14"/>
     <mergeCell ref="J51:P51"/>
     <mergeCell ref="F2:Q2"/>
@@ -16937,6 +17583,7 @@
     <mergeCell ref="AJ34:AL34"/>
     <mergeCell ref="BK34:BQ34"/>
     <mergeCell ref="J58:P58"/>
+    <mergeCell ref="A65:BQ65"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AJ49:AL49"/>
@@ -16953,12 +17600,11 @@
     <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
-    <mergeCell ref="AS65:AU65"/>
+    <mergeCell ref="AV66:AX66"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="AG35:AI35"/>
-    <mergeCell ref="AV66:AX66"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
@@ -16989,6 +17635,7 @@
     <mergeCell ref="BK64:BQ64"/>
     <mergeCell ref="J66:P66"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="AM67:AO67"/>
     <mergeCell ref="X60:AD60"/>
     <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
@@ -17001,8 +17648,8 @@
     <mergeCell ref="BB35:BD35"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
+    <mergeCell ref="AM69:AO69"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="J61:P61"/>
@@ -17011,6 +17658,7 @@
     <mergeCell ref="AM35:AO35"/>
     <mergeCell ref="AJ26:AL26"/>
     <mergeCell ref="AS13:AU13"/>
+    <mergeCell ref="E69:I69"/>
     <mergeCell ref="AP17:AR17"/>
     <mergeCell ref="Q42:W42"/>
     <mergeCell ref="A12:BQ12"/>
@@ -17029,6 +17677,7 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="BE24:BG24"/>
     <mergeCell ref="AM38:AO38"/>
+    <mergeCell ref="BH69:BJ69"/>
     <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="BH35:BJ35"/>
@@ -17049,12 +17698,14 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="AG49:AI49"/>
     <mergeCell ref="AE51:AF51"/>
+    <mergeCell ref="AV67:AX67"/>
     <mergeCell ref="BB23:BD23"/>
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="AE66:AF66"/>
     <mergeCell ref="Q45:W45"/>
+    <mergeCell ref="AV69:AX69"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
     <mergeCell ref="Q32:W32"/>
@@ -17067,7 +17718,8 @@
     <mergeCell ref="E19:I19"/>
     <mergeCell ref="AS66:AU66"/>
     <mergeCell ref="BE52:BG52"/>
-    <mergeCell ref="BK65:BQ65"/>
+    <mergeCell ref="J67:P67"/>
+    <mergeCell ref="AE67:AF67"/>
     <mergeCell ref="BK21:BQ21"/>
     <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
@@ -17075,8 +17727,10 @@
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
+    <mergeCell ref="AS68:AU68"/>
     <mergeCell ref="AJ32:AL32"/>
     <mergeCell ref="AJ63:AL63"/>
+    <mergeCell ref="J69:P69"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="Q58:W58"/>
@@ -17139,6 +17793,7 @@
     <mergeCell ref="X28:AD28"/>
     <mergeCell ref="AS30:AU30"/>
     <mergeCell ref="AG60:AI60"/>
+    <mergeCell ref="AE69:AF69"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="BH54:BJ54"/>
@@ -17147,7 +17802,7 @@
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
-    <mergeCell ref="BH65:BJ65"/>
+    <mergeCell ref="AS69:AU69"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -17167,6 +17822,7 @@
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
+    <mergeCell ref="AJ68:AL68"/>
     <mergeCell ref="AV19:AX19"/>
     <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
@@ -17178,6 +17834,7 @@
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="X43:AD43"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="Q68:W68"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
     <mergeCell ref="E15:I15"/>
@@ -17194,7 +17851,6 @@
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="B54:D54"/>
-    <mergeCell ref="AE65:AF65"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="J27:P27"/>
@@ -17228,6 +17884,7 @@
     <mergeCell ref="Q10:W11"/>
     <mergeCell ref="AP49:AR49"/>
     <mergeCell ref="E28:I28"/>
+    <mergeCell ref="BE67:BG67"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
     <mergeCell ref="BE61:BG61"/>
@@ -17240,6 +17897,7 @@
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="Q28:W28"/>
     <mergeCell ref="E30:I30"/>
+    <mergeCell ref="BE69:BG69"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
@@ -17248,12 +17906,12 @@
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
-    <mergeCell ref="AY65:BA65"/>
+    <mergeCell ref="BB66:BD66"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="E61:I61"/>
-    <mergeCell ref="BB66:BD66"/>
+    <mergeCell ref="Q67:W67"/>
     <mergeCell ref="A29:BQ29"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
@@ -17266,8 +17924,9 @@
     <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
-    <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AM66:AO66"/>
+    <mergeCell ref="BB68:BD68"/>
+    <mergeCell ref="Q69:W69"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
@@ -17281,6 +17940,7 @@
     <mergeCell ref="AE20:AF20"/>
     <mergeCell ref="BK23:BQ23"/>
     <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="AM68:AO68"/>
     <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AS27:AU27"/>
     <mergeCell ref="AP31:AR31"/>
@@ -17295,7 +17955,6 @@
     <mergeCell ref="AG28:AI28"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
-    <mergeCell ref="B65:D65"/>
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
@@ -17303,6 +17962,7 @@
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="AG67:AI67"/>
     <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
@@ -17312,6 +17972,7 @@
     <mergeCell ref="AV41:AX41"/>
     <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="AS45:AU45"/>
+    <mergeCell ref="AG69:AI69"/>
     <mergeCell ref="X53:AD53"/>
     <mergeCell ref="Q19:W19"/>
     <mergeCell ref="AS38:AU38"/>
@@ -17332,12 +17993,14 @@
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
+    <mergeCell ref="BB67:BD67"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
     <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
+    <mergeCell ref="BB69:BD69"/>
     <mergeCell ref="AG16:AI16"/>
     <mergeCell ref="E64:I64"/>
     <mergeCell ref="E51:I51"/>
@@ -17346,7 +18009,6 @@
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
-    <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
@@ -17375,13 +18037,13 @@
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE24 AE26:AE28 AE30:AE39 AE41:AE46 AE48:AE56 AE58:AE66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE24 AE26:AE28 AE30:AE39 AE41:AE46 AE48:AE56 AE58:AE64 AE66:AE69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG24 AG26:AG28 AG30:AG39 AG41:AG46 AG48:AG56 AG58:AG66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG24 AG26:AG28 AG30:AG39 AG41:AG46 AG48:AG56 AG58:AG64 AG66:AG69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV24 AV26:AV28 AV30:AV39 AV41:AV46 AV48:AV56 AV58:AV66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV24 AV26:AV28 AV30:AV39 AV41:AV46 AV48:AV56 AV58:AV64 AV66:AV69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
